--- a/outputs/Block5B_Senate_Nested_Fold_Diagnostics.xlsx
+++ b/outputs/Block5B_Senate_Nested_Fold_Diagnostics.xlsx
@@ -465,22 +465,22 @@
         <v>2006</v>
       </c>
       <c r="B2">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="C2">
-        <v>4.209288146226513</v>
+        <v>5.069159593665437</v>
       </c>
       <c r="D2">
         <v>4.924645547677709</v>
       </c>
       <c r="E2">
-        <v>4.209288146226513</v>
+        <v>4.865623570015522</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="H2" t="s">
         <v>13</v>
@@ -489,13 +489,13 @@
         <v>5.579313654851505</v>
       </c>
       <c r="J2">
-        <v>3.685780746769227</v>
+        <v>4.242390115056693</v>
       </c>
       <c r="K2">
-        <v>3.685780746769227</v>
+        <v>5.17823659291306</v>
       </c>
       <c r="L2">
-        <v>1.05088293363535</v>
+        <v>0.7322149433262219</v>
       </c>
       <c r="M2">
         <v>0.6000036573950391</v>
@@ -509,7 +509,7 @@
         <v>100</v>
       </c>
       <c r="C3">
-        <v>4.253691839821803</v>
+        <v>4.782902764624398</v>
       </c>
       <c r="D3">
         <v>4.221448579154004</v>
@@ -530,7 +530,7 @@
         <v>10.74361857330704</v>
       </c>
       <c r="J3">
-        <v>10.52453240292342</v>
+        <v>10.51886604841697</v>
       </c>
       <c r="K3">
         <v>10.74361857330704</v>
@@ -547,37 +547,37 @@
         <v>2014</v>
       </c>
       <c r="B4">
-        <v>100</v>
+        <v>0.25</v>
       </c>
       <c r="C4">
-        <v>5.616252222231791</v>
+        <v>5.342785616345073</v>
       </c>
       <c r="D4">
         <v>5.555815559393228</v>
       </c>
       <c r="E4">
-        <v>5.555815559393228</v>
+        <v>5.267749460867305</v>
       </c>
       <c r="F4">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="H4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I4">
         <v>3.630910661152456</v>
       </c>
       <c r="J4">
-        <v>3.523966190174346</v>
+        <v>3.485106815936307</v>
       </c>
       <c r="K4">
-        <v>3.630910661152456</v>
+        <v>3.381502863335457</v>
       </c>
       <c r="L4">
-        <v>1.105139068762264</v>
+        <v>0.7282257570879763</v>
       </c>
       <c r="M4">
         <v>0.6000036573950391</v>
@@ -591,19 +591,19 @@
         <v>0.25</v>
       </c>
       <c r="C5">
-        <v>4.678115427980856</v>
+        <v>5.115362240313567</v>
       </c>
       <c r="D5">
         <v>5.365909389316474</v>
       </c>
       <c r="E5">
-        <v>4.497328544976817</v>
+        <v>5.017857937181216</v>
       </c>
       <c r="F5">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="G5">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="H5" t="s">
         <v>13</v>
@@ -612,13 +612,13 @@
         <v>3.659578902902788</v>
       </c>
       <c r="J5">
-        <v>4.393383755473207</v>
+        <v>4.543570202377789</v>
       </c>
       <c r="K5">
-        <v>4.098446160475629</v>
+        <v>3.878601788930343</v>
       </c>
       <c r="L5">
-        <v>0.8767161928199414</v>
+        <v>0.756804455446531</v>
       </c>
       <c r="M5">
         <v>0.6000036573950391</v>
@@ -632,19 +632,19 @@
         <v>1</v>
       </c>
       <c r="C6">
-        <v>4.733966455529235</v>
+        <v>4.461424323931116</v>
       </c>
       <c r="D6">
         <v>5.073481209271587</v>
       </c>
       <c r="E6">
-        <v>4.584140509887185</v>
+        <v>4.461424323931116</v>
       </c>
       <c r="F6">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="G6">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="H6" t="s">
         <v>13</v>
@@ -653,13 +653,13 @@
         <v>5.565711268516627</v>
       </c>
       <c r="J6">
-        <v>4.028977292767414</v>
+        <v>5.122173389106289</v>
       </c>
       <c r="K6">
-        <v>4.413160786704718</v>
+        <v>5.122173389106289</v>
       </c>
       <c r="L6">
-        <v>0.8685777615482337</v>
+        <v>1.104774690006878</v>
       </c>
       <c r="M6">
         <v>0.6000036573950391</v>
